--- a/artfynd/A 58343-2025 artfynd.xlsx
+++ b/artfynd/A 58343-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129950376</v>
       </c>
       <c r="B2" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,42 +781,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129950368</v>
+        <v>129950390</v>
       </c>
       <c r="B3" t="n">
-        <v>98790</v>
+        <v>57895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,13 +828,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581210</v>
+        <v>581396</v>
       </c>
       <c r="R3" t="n">
-        <v>6430835</v>
+        <v>6431028</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,7 +872,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,46 +890,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129950390</v>
+        <v>129950368</v>
       </c>
       <c r="B4" t="n">
-        <v>57896</v>
+        <v>98794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -934,13 +933,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581396</v>
+        <v>581210</v>
       </c>
       <c r="R4" t="n">
-        <v>6431028</v>
+        <v>6430835</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,6 +977,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -999,7 +999,7 @@
         <v>129950385</v>
       </c>
       <c r="B5" t="n">
-        <v>91620</v>
+        <v>91623</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>129950485</v>
       </c>
       <c r="B6" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129950423</v>
+        <v>129950410</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>57895</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,26 +1226,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1298,11 +1298,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Kom flygande från V och satte sig i tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129950410</v>
+        <v>129950423</v>
       </c>
       <c r="B8" t="n">
-        <v>57896</v>
+        <v>57734</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1340,26 +1335,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1412,6 +1407,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Kom flygande från V och satte sig i tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 58343-2025 artfynd.xlsx
+++ b/artfynd/A 58343-2025 artfynd.xlsx
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129950410</v>
+        <v>129950423</v>
       </c>
       <c r="B7" t="n">
-        <v>57895</v>
+        <v>57734</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,26 +1226,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1298,6 +1298,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Kom flygande från V och satte sig i tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129950423</v>
+        <v>129950410</v>
       </c>
       <c r="B8" t="n">
-        <v>57734</v>
+        <v>57895</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1335,26 +1340,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1407,11 +1412,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Kom flygande från V och satte sig i tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 58343-2025 artfynd.xlsx
+++ b/artfynd/A 58343-2025 artfynd.xlsx
@@ -781,46 +781,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129950390</v>
+        <v>129950368</v>
       </c>
       <c r="B3" t="n">
-        <v>57895</v>
+        <v>98794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,13 +824,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581396</v>
+        <v>581210</v>
       </c>
       <c r="R3" t="n">
-        <v>6431028</v>
+        <v>6430835</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,6 +868,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -890,42 +887,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129950368</v>
+        <v>129950390</v>
       </c>
       <c r="B4" t="n">
-        <v>98794</v>
+        <v>57895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -933,13 +934,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581210</v>
+        <v>581396</v>
       </c>
       <c r="R4" t="n">
-        <v>6430835</v>
+        <v>6431028</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,7 +978,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -996,59 +996,60 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129950385</v>
+        <v>129950485</v>
       </c>
       <c r="B5" t="n">
-        <v>91623</v>
+        <v>98794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 58343, S körserum, Sm</t>
+          <t>A 58343, Skörserum, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581400</v>
+        <v>581084</v>
       </c>
       <c r="R5" t="n">
-        <v>6431002</v>
+        <v>6431150</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,60 +1106,59 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129950485</v>
+        <v>129950385</v>
       </c>
       <c r="B6" t="n">
-        <v>98794</v>
+        <v>91623</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 58343, Skörserum, Sm</t>
+          <t>A 58343, S körserum, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581084</v>
+        <v>581400</v>
       </c>
       <c r="R6" t="n">
-        <v>6431150</v>
+        <v>6431002</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 58343-2025 artfynd.xlsx
+++ b/artfynd/A 58343-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129950376</v>
       </c>
       <c r="B2" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,42 +781,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129950368</v>
+        <v>129950390</v>
       </c>
       <c r="B3" t="n">
-        <v>98794</v>
+        <v>57898</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,13 +828,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581210</v>
+        <v>581396</v>
       </c>
       <c r="R3" t="n">
-        <v>6430835</v>
+        <v>6431028</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,7 +872,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,46 +890,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129950390</v>
+        <v>129950368</v>
       </c>
       <c r="B4" t="n">
-        <v>57895</v>
+        <v>98797</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -934,13 +933,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581396</v>
+        <v>581210</v>
       </c>
       <c r="R4" t="n">
-        <v>6431028</v>
+        <v>6430835</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,6 +977,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -996,60 +996,59 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129950485</v>
+        <v>129950385</v>
       </c>
       <c r="B5" t="n">
-        <v>98794</v>
+        <v>91626</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 58343, Skörserum, Sm</t>
+          <t>A 58343, S körserum, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581084</v>
+        <v>581400</v>
       </c>
       <c r="R5" t="n">
-        <v>6431150</v>
+        <v>6431002</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,59 +1105,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129950385</v>
+        <v>129950485</v>
       </c>
       <c r="B6" t="n">
-        <v>91623</v>
+        <v>98797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 58343, S körserum, Sm</t>
+          <t>A 58343, Skörserum, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581400</v>
+        <v>581084</v>
       </c>
       <c r="R6" t="n">
-        <v>6431002</v>
+        <v>6431150</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>129950423</v>
       </c>
       <c r="B7" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>129950410</v>
       </c>
       <c r="B8" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 58343-2025 artfynd.xlsx
+++ b/artfynd/A 58343-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129950376</v>
       </c>
       <c r="B2" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,46 +781,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129950390</v>
+        <v>129950368</v>
       </c>
       <c r="B3" t="n">
-        <v>57898</v>
+        <v>98798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,13 +824,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581396</v>
+        <v>581210</v>
       </c>
       <c r="R3" t="n">
-        <v>6431028</v>
+        <v>6430835</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,6 +868,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -890,42 +887,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129950368</v>
+        <v>129950390</v>
       </c>
       <c r="B4" t="n">
-        <v>98797</v>
+        <v>57898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -933,13 +934,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581210</v>
+        <v>581396</v>
       </c>
       <c r="R4" t="n">
-        <v>6430835</v>
+        <v>6431028</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,7 +978,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -999,7 +999,7 @@
         <v>129950385</v>
       </c>
       <c r="B5" t="n">
-        <v>91626</v>
+        <v>91627</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>129950485</v>
       </c>
       <c r="B6" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58343-2025 artfynd.xlsx
+++ b/artfynd/A 58343-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129950376</v>
       </c>
       <c r="B2" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129950368</v>
       </c>
       <c r="B3" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129950390</v>
       </c>
       <c r="B4" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129950385</v>
       </c>
       <c r="B5" t="n">
-        <v>91627</v>
+        <v>91644</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>129950485</v>
       </c>
       <c r="B6" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>129950410</v>
       </c>
       <c r="B8" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 58343-2025 artfynd.xlsx
+++ b/artfynd/A 58343-2025 artfynd.xlsx
@@ -996,60 +996,59 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129950485</v>
+        <v>129950385</v>
       </c>
       <c r="B5" t="n">
-        <v>98831</v>
+        <v>91660</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 58343, Skörserum, Sm</t>
+          <t>A 58343, S körserum, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581084</v>
+        <v>581400</v>
       </c>
       <c r="R5" t="n">
-        <v>6431150</v>
+        <v>6431002</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,59 +1105,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129950385</v>
+        <v>129950485</v>
       </c>
       <c r="B6" t="n">
-        <v>91660</v>
+        <v>98831</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 58343, S körserum, Sm</t>
+          <t>A 58343, Skörserum, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581400</v>
+        <v>581084</v>
       </c>
       <c r="R6" t="n">
-        <v>6431002</v>
+        <v>6431150</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 58343-2025 artfynd.xlsx
+++ b/artfynd/A 58343-2025 artfynd.xlsx
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129950423</v>
+        <v>129950410</v>
       </c>
       <c r="B7" t="n">
-        <v>57738</v>
+        <v>57900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,26 +1226,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1298,11 +1298,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Kom flygande från V och satte sig i tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129950410</v>
+        <v>129950423</v>
       </c>
       <c r="B8" t="n">
-        <v>57900</v>
+        <v>57738</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1340,26 +1335,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1412,6 +1407,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Kom flygande från V och satte sig i tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 58343-2025 artfynd.xlsx
+++ b/artfynd/A 58343-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129950376</v>
       </c>
       <c r="B2" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>129950368</v>
       </c>
       <c r="B4" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,59 +996,60 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129950385</v>
+        <v>129950485</v>
       </c>
       <c r="B5" t="n">
-        <v>91660</v>
+        <v>98833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 58343, S körserum, Sm</t>
+          <t>A 58343, Skörserum, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581400</v>
+        <v>581084</v>
       </c>
       <c r="R5" t="n">
-        <v>6431002</v>
+        <v>6431150</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,60 +1106,59 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129950485</v>
+        <v>129950385</v>
       </c>
       <c r="B6" t="n">
-        <v>98831</v>
+        <v>91662</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 58343, Skörserum, Sm</t>
+          <t>A 58343, S körserum, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581084</v>
+        <v>581400</v>
       </c>
       <c r="R6" t="n">
-        <v>6431150</v>
+        <v>6431002</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 58343-2025 artfynd.xlsx
+++ b/artfynd/A 58343-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129950376</v>
       </c>
       <c r="B2" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129950390</v>
       </c>
       <c r="B3" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>129950368</v>
       </c>
       <c r="B4" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,60 +996,59 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129950485</v>
+        <v>129950385</v>
       </c>
       <c r="B5" t="n">
-        <v>98833</v>
+        <v>91749</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 58343, Skörserum, Sm</t>
+          <t>A 58343, S körserum, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581084</v>
+        <v>581400</v>
       </c>
       <c r="R5" t="n">
-        <v>6431150</v>
+        <v>6431002</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,59 +1105,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129950385</v>
+        <v>129950485</v>
       </c>
       <c r="B6" t="n">
-        <v>91662</v>
+        <v>98920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 58343, S körserum, Sm</t>
+          <t>A 58343, Skörserum, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581400</v>
+        <v>581084</v>
       </c>
       <c r="R6" t="n">
-        <v>6431002</v>
+        <v>6431150</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129950410</v>
+        <v>129950423</v>
       </c>
       <c r="B7" t="n">
-        <v>57900</v>
+        <v>57823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,26 +1226,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1298,6 +1298,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Kom flygande från V och satte sig i tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129950423</v>
+        <v>129950410</v>
       </c>
       <c r="B8" t="n">
-        <v>57738</v>
+        <v>57985</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1335,26 +1340,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1407,11 +1412,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Kom flygande från V och satte sig i tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 58343-2025 artfynd.xlsx
+++ b/artfynd/A 58343-2025 artfynd.xlsx
@@ -781,46 +781,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129950390</v>
+        <v>129950368</v>
       </c>
       <c r="B3" t="n">
-        <v>57985</v>
+        <v>98920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,13 +824,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581396</v>
+        <v>581210</v>
       </c>
       <c r="R3" t="n">
-        <v>6431028</v>
+        <v>6430835</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,6 +868,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -890,42 +887,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129950368</v>
+        <v>129950390</v>
       </c>
       <c r="B4" t="n">
-        <v>98920</v>
+        <v>57985</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -933,13 +934,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581210</v>
+        <v>581396</v>
       </c>
       <c r="R4" t="n">
-        <v>6430835</v>
+        <v>6431028</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,7 +978,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -996,59 +996,60 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129950385</v>
+        <v>129950485</v>
       </c>
       <c r="B5" t="n">
-        <v>91749</v>
+        <v>98920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 58343, S körserum, Sm</t>
+          <t>A 58343, Skörserum, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581400</v>
+        <v>581084</v>
       </c>
       <c r="R5" t="n">
-        <v>6431002</v>
+        <v>6431150</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,60 +1106,59 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129950485</v>
+        <v>129950385</v>
       </c>
       <c r="B6" t="n">
-        <v>98920</v>
+        <v>91749</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 58343, Skörserum, Sm</t>
+          <t>A 58343, S körserum, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581084</v>
+        <v>581400</v>
       </c>
       <c r="R6" t="n">
-        <v>6431150</v>
+        <v>6431002</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 58343-2025 artfynd.xlsx
+++ b/artfynd/A 58343-2025 artfynd.xlsx
@@ -781,42 +781,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129950368</v>
+        <v>129950390</v>
       </c>
       <c r="B3" t="n">
-        <v>98920</v>
+        <v>57985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,13 +828,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581210</v>
+        <v>581396</v>
       </c>
       <c r="R3" t="n">
-        <v>6430835</v>
+        <v>6431028</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,7 +872,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,46 +890,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129950390</v>
+        <v>129950368</v>
       </c>
       <c r="B4" t="n">
-        <v>57985</v>
+        <v>98920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -934,13 +933,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581396</v>
+        <v>581210</v>
       </c>
       <c r="R4" t="n">
-        <v>6431028</v>
+        <v>6430835</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,6 +977,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -996,60 +996,59 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129950485</v>
+        <v>129950385</v>
       </c>
       <c r="B5" t="n">
-        <v>98920</v>
+        <v>91749</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 58343, Skörserum, Sm</t>
+          <t>A 58343, S körserum, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581084</v>
+        <v>581400</v>
       </c>
       <c r="R5" t="n">
-        <v>6431150</v>
+        <v>6431002</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,59 +1105,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129950385</v>
+        <v>129950485</v>
       </c>
       <c r="B6" t="n">
-        <v>91749</v>
+        <v>98920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 58343, S körserum, Sm</t>
+          <t>A 58343, Skörserum, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581400</v>
+        <v>581084</v>
       </c>
       <c r="R6" t="n">
-        <v>6431002</v>
+        <v>6431150</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 58343-2025 artfynd.xlsx
+++ b/artfynd/A 58343-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129950376</v>
       </c>
       <c r="B2" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129950390</v>
       </c>
       <c r="B3" t="n">
-        <v>57985</v>
+        <v>57900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>129950368</v>
       </c>
       <c r="B4" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,59 +996,60 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129950385</v>
+        <v>129950485</v>
       </c>
       <c r="B5" t="n">
-        <v>91749</v>
+        <v>98833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 58343, S körserum, Sm</t>
+          <t>A 58343, Skörserum, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581400</v>
+        <v>581084</v>
       </c>
       <c r="R5" t="n">
-        <v>6431002</v>
+        <v>6431150</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,60 +1106,59 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129950485</v>
+        <v>129950385</v>
       </c>
       <c r="B6" t="n">
-        <v>98920</v>
+        <v>91662</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 58343, Skörserum, Sm</t>
+          <t>A 58343, S körserum, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581084</v>
+        <v>581400</v>
       </c>
       <c r="R6" t="n">
-        <v>6431150</v>
+        <v>6431002</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129950423</v>
+        <v>129950410</v>
       </c>
       <c r="B7" t="n">
-        <v>57823</v>
+        <v>57900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,26 +1226,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1298,11 +1298,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Kom flygande från V och satte sig i tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129950410</v>
+        <v>129950423</v>
       </c>
       <c r="B8" t="n">
-        <v>57985</v>
+        <v>57738</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1340,26 +1335,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1412,6 +1407,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Kom flygande från V och satte sig i tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 58343-2025 artfynd.xlsx
+++ b/artfynd/A 58343-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>129950423</v>
       </c>
       <c r="B7" t="n">
-        <v>57881</v>
+        <v>57823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 58343-2025 artfynd.xlsx
+++ b/artfynd/A 58343-2025 artfynd.xlsx
@@ -675,53 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129950376</v>
+        <v>129950385</v>
       </c>
       <c r="B2" t="n">
-        <v>98920</v>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 58343, Skörserum, Sm</t>
+          <t>A 58343, S körserum, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581216</v>
+        <v>581400</v>
       </c>
       <c r="R2" t="n">
-        <v>6430820</v>
+        <v>6431002</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,32 +784,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129950390</v>
+        <v>129950423</v>
       </c>
       <c r="B3" t="n">
-        <v>57985</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -828,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581396</v>
+        <v>581296</v>
       </c>
       <c r="R3" t="n">
-        <v>6431028</v>
+        <v>6431018</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,6 +867,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Kom flygande från V och satte sig i tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,42 +898,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129950368</v>
+        <v>129950390</v>
       </c>
       <c r="B4" t="n">
-        <v>98920</v>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -933,13 +945,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581210</v>
+        <v>581396</v>
       </c>
       <c r="R4" t="n">
-        <v>6430835</v>
+        <v>6431028</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,7 +989,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -996,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129950385</v>
+        <v>129950410</v>
       </c>
       <c r="B5" t="n">
-        <v>91749</v>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,48 +1018,49 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 58343, S körserum, Sm</t>
+          <t>A 58343, Skörserum, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581400</v>
+        <v>581296</v>
       </c>
       <c r="R5" t="n">
-        <v>6431002</v>
+        <v>6431018</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1098,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1105,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129950485</v>
+        <v>129950368</v>
       </c>
       <c r="B6" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,11 +1144,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1152,13 +1159,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581084</v>
+        <v>581210</v>
       </c>
       <c r="R6" t="n">
-        <v>6431150</v>
+        <v>6430835</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,46 +1222,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129950423</v>
+        <v>129950376</v>
       </c>
       <c r="B7" t="n">
-        <v>57823</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1262,13 +1265,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581296</v>
+        <v>581216</v>
       </c>
       <c r="R7" t="n">
-        <v>6431018</v>
+        <v>6430820</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1300,17 +1303,13 @@
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Kom flygande från V och satte sig i tall.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1329,46 +1328,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129950410</v>
+        <v>129950485</v>
       </c>
       <c r="B8" t="n">
-        <v>57985</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1376,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581296</v>
+        <v>581084</v>
       </c>
       <c r="R8" t="n">
-        <v>6431018</v>
+        <v>6431150</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1420,6 +1419,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
